--- a/Excel Project/Sales_Performance_Dashboard.xlsx
+++ b/Excel Project/Sales_Performance_Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8cc568375f747077/Documents/Projects/Excel Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\DA projects\Excel Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="803" documentId="8_{1BB484AA-C773-4A24-9A00-72D977B43675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECDC815C-EE89-4DB2-8F96-C05FF3E98B5E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2ADEE3-27C8-4D74-9CC5-E947EAE3F366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SalesData" sheetId="1" r:id="rId1"/>
@@ -2339,7 +2339,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2384,7 +2384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2425,32 +2425,26 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4429,435 +4423,6 @@
               <a:rPr lang="en-US" sz="1600">
                 <a:latin typeface="Aptos ExtraBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t>Top 10 Products by Sales</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.34731933508311463"/>
-          <c:y val="7.7682997958588504E-2"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:delete val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:delete val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:delete val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:delete val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.49540827419028644"/>
-          <c:y val="0.24241709076899182"/>
-          <c:w val="0.34897635229763974"/>
-          <c:h val="0.57724390976958284"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>Total</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:cat>
-            <c:strLit>
-              <c:ptCount val="10"/>
-              <c:pt idx="0">
-                <c:v>Bush Somerset Collection Bookcase</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>Canon ImageCLASS Printer</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>Cisco SPA 501G IP Phone</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>Coin Envelopes</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>Desk Organizer</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>Holmes Replacement Filter</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>HP LaserJet Printer</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>Logitech Wireless Mouse</c:v>
-              </c:pt>
-              <c:pt idx="8">
-                <c:v>Office Star Mesh Chair</c:v>
-              </c:pt>
-              <c:pt idx="9">
-                <c:v>Sharp Digital Copier</c:v>
-              </c:pt>
-            </c:strLit>
-          </c:cat>
-          <c:val>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="10"/>
-              <c:pt idx="0">
-                <c:v>18871.009999999998</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>20600.689999999999</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>14446.5</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>18676.900000000001</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>27979.359999999997</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>18730.39</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>21598.12</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>24902.76</c:v>
-              </c:pt>
-              <c:pt idx="8">
-                <c:v>14385.330000000002</c:v>
-              </c:pt>
-              <c:pt idx="9">
-                <c:v>15255.890000000001</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-5F1B-4519-983C-5B12BF982AC3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="1912914048"/>
-        <c:axId val="1874961776"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1912914048"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1874961776"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1874961776"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1912914048"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="accent5">
-        <a:lumMod val="20000"/>
-        <a:lumOff val="80000"/>
-      </a:schemeClr>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst/>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1600">
-                <a:latin typeface="Aptos ExtraBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-              </a:rPr>
               <a:t>Sales</a:t>
             </a:r>
             <a:r>
@@ -5086,8 +4651,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.31068423260388106"/>
-          <c:y val="0.23671049117255594"/>
+          <c:x val="0.27579196219022351"/>
+          <c:y val="0.23671043876568709"/>
           <c:w val="0.61042098874952166"/>
           <c:h val="0.61180916762086313"/>
         </c:manualLayout>
@@ -5364,7 +4929,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5666,8 +5231,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.21555586400643836"/>
-          <c:y val="0.24130936582238"/>
+          <c:x val="0.21555587868005543"/>
+          <c:y val="0.22650373273674831"/>
           <c:w val="0.64994860017497813"/>
           <c:h val="0.53774387576552929"/>
         </c:manualLayout>
@@ -5898,101 +5463,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
-  <cx:chartData>
-    <cx:data id="0">
-      <cx:strDim type="cat">
-        <cx:lvl ptCount="0"/>
-      </cx:strDim>
-      <cx:numDim type="val">
-        <cx:lvl ptCount="0"/>
-      </cx:numDim>
-    </cx:data>
-  </cx:chartData>
-  <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0">
-      <cx:tx>
-        <cx:txData>
-          <cx:v>Category Analysis</cx:v>
-        </cx:txData>
-      </cx:tx>
-      <cx:txPr>
-        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr>
-              <a:latin typeface="Aptos ExtraBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Aptos ExtraBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Aptos ExtraBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:latin typeface="Aptos ExtraBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Category Analysis</a:t>
-          </a:r>
-        </a:p>
-      </cx:txPr>
-    </cx:title>
-    <cx:plotArea>
-      <cx:plotAreaRegion>
-        <cx:plotSurface>
-          <cx:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5">
-                <a:lumMod val="20000"/>
-                <a:lumOff val="80000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </cx:spPr>
-        </cx:plotSurface>
-        <cx:series layoutId="funnel" uniqueId="{3AB389A1-F205-4AA4-AF30-6F483B4D8DAB}">
-          <cx:dataLabels>
-            <cx:visibility seriesName="0" categoryName="0" value="1"/>
-          </cx:dataLabels>
-          <cx:dataId val="0"/>
-        </cx:series>
-      </cx:plotAreaRegion>
-      <cx:axis id="0">
-        <cx:catScaling gapWidth="0.150000006"/>
-        <cx:tickLabels/>
-        <cx:txPr>
-          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1100">
-                <a:latin typeface="Aptos ExtraBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Aptos ExtraBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Aptos ExtraBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:latin typeface="Aptos ExtraBold" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:endParaRPr>
-          </a:p>
-        </cx:txPr>
-      </cx:axis>
-    </cx:plotArea>
-  </cx:chart>
-</cx:chartSpace>
-</file>
-
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -6114,46 +5584,6 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -8214,573 +7644,18 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="424">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-          <a:gs pos="39000">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="lt1">
-              <a:lumMod val="75000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-          <a:alpha val="75000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="50000"/>
-          <a:lumOff val="50000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-                <a:lumOff val="10000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-                <a:lumOff val="10000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1">
-          <a:lumMod val="95000"/>
-          <a:alpha val="39000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat">
-        <a:solidFill>
-          <a:schemeClr val="bg1">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1800" b="1"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>359141</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>42316</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>218606</xdr:colOff>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>171762</xdr:rowOff>
     </xdr:to>
@@ -8811,16 +7686,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>93689</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>538189</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>175979</xdr:rowOff>
+      <xdr:rowOff>87079</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>327910</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>46845</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>148445</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8849,23 +7724,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>546516</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>91033</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>88899</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>265609</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>31229</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>148828</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EBF8C9E-DAEF-4035-AC77-BA6F9D2D755E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{601FC8B0-DA30-40E8-8F3D-FF265DCA36B5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8887,54 +7762,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>46844</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>121796</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>67247</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>265450</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>185503</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{601FC8B0-DA30-40E8-8F3D-FF265DCA36B5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>312296</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>156147</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>593360</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>62460</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8955,105 +7792,27 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>46843</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>152885</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>46845</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:cx2="http://schemas.microsoft.com/office/drawing/2015/10/21/chartex" Requires="cx2">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="7" name="Chart 6">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4240810-4A9D-49CE-B920-CFE07C3FA244}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="0" y="1723243"/>
-              <a:ext cx="4353410" cy="5724527"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-IN" sz="1100"/>
-                <a:t>This chart isn't available in your version of Excel.
-Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>97456</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>122707</xdr:rowOff>
+      <xdr:rowOff>8407</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>434733</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>136362</xdr:rowOff>
+      <xdr:colOff>337277</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>9362</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="8" name="Year">
@@ -9076,7 +7835,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -9086,8 +7845,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="97456" y="10315694"/>
-              <a:ext cx="2477309" cy="1126967"/>
+              <a:off x="0" y="1696930"/>
+              <a:ext cx="2476072" cy="1152614"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -9119,19 +7878,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>202929</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>132103</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>280674</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>180187</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>342901</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1593</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="10" name="Category">
@@ -9154,7 +7913,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -9164,8 +7923,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2788286" y="10325090"/>
-              <a:ext cx="2848654" cy="1161396"/>
+              <a:off x="1" y="2972285"/>
+              <a:ext cx="2481695" cy="1202990"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -9197,19 +7956,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>511665</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>149276</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>174676</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>449709</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>168088</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>2988</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="11" name="State">
@@ -9232,7 +7991,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -9242,8 +8001,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5867931" y="10342263"/>
-              <a:ext cx="2968726" cy="1132124"/>
+              <a:off x="0" y="4348358"/>
+              <a:ext cx="2519795" cy="1161812"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -9275,19 +8034,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>608052</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>112059</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>61259</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>258803</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>168088</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>381001</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>117288</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="12" name="Order Status">
@@ -9310,7 +8069,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -9320,8 +8079,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8995000" y="10305046"/>
-              <a:ext cx="3287569" cy="1169341"/>
+              <a:off x="1" y="5758941"/>
+              <a:ext cx="2519795" cy="1199029"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -19103,8 +17862,8 @@
     <tabular pivotCacheId="678100836">
       <items count="3">
         <i x="0" s="1"/>
-        <i x="1"/>
-        <i x="2"/>
+        <i x="1" s="1"/>
+        <i x="2" s="1"/>
       </items>
     </tabular>
   </data>
@@ -47182,50 +45941,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>731</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
     </row>
     <row r="2" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
     </row>
     <row r="3" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
@@ -47241,9 +46000,9 @@
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="12"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
       <c r="Q3" s="16"/>
       <c r="R3" s="9"/>
       <c r="S3" s="9"/>
@@ -47264,9 +46023,9 @@
       <c r="L4" s="9"/>
       <c r="M4" s="9"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
@@ -47295,33 +46054,33 @@
     </row>
     <row r="6" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="21" t="s">
         <v>732</v>
       </c>
-      <c r="C6" s="23"/>
+      <c r="C6" s="21"/>
       <c r="D6" s="17"/>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="21" t="s">
         <v>734</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="21"/>
       <c r="G6" s="16"/>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="21" t="s">
         <v>736</v>
       </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
       <c r="K6" s="17"/>
-      <c r="L6" s="23" t="s">
+      <c r="L6" s="21" t="s">
         <v>733</v>
       </c>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="23" t="s">
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="21" t="s">
         <v>735</v>
       </c>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="Q6" s="21"/>
+      <c r="R6" s="21"/>
       <c r="S6" s="16"/>
       <c r="T6" s="9"/>
     </row>
@@ -47339,26 +46098,26 @@
       </c>
       <c r="F7" s="25"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18">
+      <c r="H7" s="26"/>
+      <c r="I7" s="26">
         <f>COUNTA(_xlfn.UNIQUE(Table2[Customer Name]))</f>
         <v>20</v>
       </c>
-      <c r="J7" s="20"/>
+      <c r="J7" s="9"/>
       <c r="K7" s="12"/>
-      <c r="L7" s="27">
+      <c r="L7" s="22">
         <f>COUNTA(SalesData!A2:A601)</f>
         <v>600</v>
       </c>
-      <c r="M7" s="27"/>
-      <c r="N7" s="27"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
       <c r="O7" s="11"/>
-      <c r="P7" s="27">
+      <c r="P7" s="22">
         <f>SUM(Table2[Sales])/SUM(Table2[Profit])</f>
         <v>2.7618927836464353</v>
       </c>
-      <c r="Q7" s="27"/>
-      <c r="R7" s="27"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
       <c r="S7" s="12"/>
       <c r="T7" s="9"/>
     </row>
@@ -48045,510 +46804,510 @@
       <c r="T38" s="9"/>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="9"/>
-      <c r="R39" s="9"/>
-      <c r="S39" s="9"/>
-      <c r="T39" s="9"/>
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="23"/>
+      <c r="K39" s="23"/>
+      <c r="L39" s="23"/>
+      <c r="M39" s="23"/>
+      <c r="N39" s="23"/>
+      <c r="O39" s="23"/>
+      <c r="P39" s="23"/>
+      <c r="Q39" s="23"/>
+      <c r="R39" s="23"/>
+      <c r="S39" s="23"/>
+      <c r="T39" s="23"/>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="9"/>
-      <c r="Q40" s="9"/>
-      <c r="R40" s="9"/>
-      <c r="S40" s="9"/>
-      <c r="T40" s="9"/>
+      <c r="A40" s="23"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="23"/>
+      <c r="K40" s="23"/>
+      <c r="L40" s="23"/>
+      <c r="M40" s="23"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="23"/>
+      <c r="P40" s="23"/>
+      <c r="Q40" s="23"/>
+      <c r="R40" s="23"/>
+      <c r="S40" s="23"/>
+      <c r="T40" s="23"/>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="9"/>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
+      <c r="A41" s="23"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="23"/>
+      <c r="K41" s="23"/>
+      <c r="L41" s="23"/>
+      <c r="M41" s="23"/>
+      <c r="N41" s="23"/>
+      <c r="O41" s="23"/>
+      <c r="P41" s="23"/>
+      <c r="Q41" s="23"/>
+      <c r="R41" s="23"/>
+      <c r="S41" s="23"/>
+      <c r="T41" s="23"/>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="9"/>
-      <c r="R42" s="9"/>
-      <c r="S42" s="9"/>
-      <c r="T42" s="9"/>
+      <c r="A42" s="23"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="23"/>
+      <c r="K42" s="23"/>
+      <c r="L42" s="23"/>
+      <c r="M42" s="23"/>
+      <c r="N42" s="23"/>
+      <c r="O42" s="23"/>
+      <c r="P42" s="23"/>
+      <c r="Q42" s="23"/>
+      <c r="R42" s="23"/>
+      <c r="S42" s="23"/>
+      <c r="T42" s="23"/>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
-      <c r="P43" s="9"/>
-      <c r="Q43" s="9"/>
-      <c r="R43" s="9"/>
-      <c r="S43" s="9"/>
-      <c r="T43" s="9"/>
+      <c r="A43" s="23"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="23"/>
+      <c r="K43" s="23"/>
+      <c r="L43" s="23"/>
+      <c r="M43" s="23"/>
+      <c r="N43" s="23"/>
+      <c r="O43" s="23"/>
+      <c r="P43" s="23"/>
+      <c r="Q43" s="23"/>
+      <c r="R43" s="23"/>
+      <c r="S43" s="23"/>
+      <c r="T43" s="23"/>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
-      <c r="P44" s="9"/>
-      <c r="Q44" s="9"/>
-      <c r="R44" s="9"/>
-      <c r="S44" s="9"/>
-      <c r="T44" s="9"/>
+      <c r="A44" s="23"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="23"/>
+      <c r="J44" s="23"/>
+      <c r="K44" s="23"/>
+      <c r="L44" s="23"/>
+      <c r="M44" s="23"/>
+      <c r="N44" s="23"/>
+      <c r="O44" s="23"/>
+      <c r="P44" s="23"/>
+      <c r="Q44" s="23"/>
+      <c r="R44" s="23"/>
+      <c r="S44" s="23"/>
+      <c r="T44" s="23"/>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="9"/>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
-      <c r="P45" s="9"/>
-      <c r="Q45" s="9"/>
-      <c r="R45" s="9"/>
-      <c r="S45" s="9"/>
-      <c r="T45" s="9"/>
+      <c r="A45" s="23"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="23"/>
+      <c r="I45" s="23"/>
+      <c r="J45" s="23"/>
+      <c r="K45" s="23"/>
+      <c r="L45" s="23"/>
+      <c r="M45" s="23"/>
+      <c r="N45" s="23"/>
+      <c r="O45" s="23"/>
+      <c r="P45" s="23"/>
+      <c r="Q45" s="23"/>
+      <c r="R45" s="23"/>
+      <c r="S45" s="23"/>
+      <c r="T45" s="23"/>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="9"/>
-      <c r="J46" s="9"/>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
-      <c r="M46" s="9"/>
-      <c r="N46" s="9"/>
-      <c r="O46" s="9"/>
-      <c r="P46" s="9"/>
-      <c r="Q46" s="9"/>
-      <c r="R46" s="9"/>
-      <c r="S46" s="9"/>
-      <c r="T46" s="9"/>
+      <c r="A46" s="23"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="23"/>
+      <c r="J46" s="23"/>
+      <c r="K46" s="23"/>
+      <c r="L46" s="23"/>
+      <c r="M46" s="23"/>
+      <c r="N46" s="23"/>
+      <c r="O46" s="23"/>
+      <c r="P46" s="23"/>
+      <c r="Q46" s="23"/>
+      <c r="R46" s="23"/>
+      <c r="S46" s="23"/>
+      <c r="T46" s="23"/>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="9"/>
-      <c r="K47" s="9"/>
-      <c r="L47" s="9"/>
-      <c r="M47" s="9"/>
-      <c r="N47" s="9"/>
-      <c r="O47" s="9"/>
-      <c r="P47" s="9"/>
-      <c r="Q47" s="9"/>
-      <c r="R47" s="9"/>
-      <c r="S47" s="9"/>
-      <c r="T47" s="9"/>
+      <c r="A47" s="23"/>
+      <c r="B47" s="23"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="23"/>
+      <c r="I47" s="23"/>
+      <c r="J47" s="23"/>
+      <c r="K47" s="23"/>
+      <c r="L47" s="23"/>
+      <c r="M47" s="23"/>
+      <c r="N47" s="23"/>
+      <c r="O47" s="23"/>
+      <c r="P47" s="23"/>
+      <c r="Q47" s="23"/>
+      <c r="R47" s="23"/>
+      <c r="S47" s="23"/>
+      <c r="T47" s="23"/>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="9"/>
-      <c r="J48" s="9"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
-      <c r="M48" s="9"/>
-      <c r="N48" s="9"/>
-      <c r="O48" s="9"/>
-      <c r="P48" s="9"/>
-      <c r="Q48" s="9"/>
-      <c r="R48" s="9"/>
-      <c r="S48" s="9"/>
-      <c r="T48" s="9"/>
+      <c r="A48" s="23"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="23"/>
+      <c r="G48" s="23"/>
+      <c r="H48" s="23"/>
+      <c r="I48" s="23"/>
+      <c r="J48" s="23"/>
+      <c r="K48" s="23"/>
+      <c r="L48" s="23"/>
+      <c r="M48" s="23"/>
+      <c r="N48" s="23"/>
+      <c r="O48" s="23"/>
+      <c r="P48" s="23"/>
+      <c r="Q48" s="23"/>
+      <c r="R48" s="23"/>
+      <c r="S48" s="23"/>
+      <c r="T48" s="23"/>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="9"/>
-      <c r="J49" s="9"/>
-      <c r="K49" s="9"/>
-      <c r="L49" s="9"/>
-      <c r="M49" s="9"/>
-      <c r="N49" s="9"/>
-      <c r="O49" s="9"/>
-      <c r="P49" s="9"/>
-      <c r="Q49" s="9"/>
-      <c r="R49" s="9"/>
-      <c r="S49" s="9"/>
-      <c r="T49" s="9"/>
+      <c r="A49" s="23"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="23"/>
+      <c r="J49" s="23"/>
+      <c r="K49" s="23"/>
+      <c r="L49" s="23"/>
+      <c r="M49" s="23"/>
+      <c r="N49" s="23"/>
+      <c r="O49" s="23"/>
+      <c r="P49" s="23"/>
+      <c r="Q49" s="23"/>
+      <c r="R49" s="23"/>
+      <c r="S49" s="23"/>
+      <c r="T49" s="23"/>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="9"/>
-      <c r="J50" s="9"/>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
-      <c r="M50" s="9"/>
-      <c r="N50" s="9"/>
-      <c r="O50" s="9"/>
-      <c r="P50" s="9"/>
-      <c r="Q50" s="9"/>
-      <c r="R50" s="9"/>
-      <c r="S50" s="9"/>
-      <c r="T50" s="9"/>
+      <c r="A50" s="23"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="23"/>
+      <c r="J50" s="23"/>
+      <c r="K50" s="23"/>
+      <c r="L50" s="23"/>
+      <c r="M50" s="23"/>
+      <c r="N50" s="23"/>
+      <c r="O50" s="23"/>
+      <c r="P50" s="23"/>
+      <c r="Q50" s="23"/>
+      <c r="R50" s="23"/>
+      <c r="S50" s="23"/>
+      <c r="T50" s="23"/>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="9"/>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
-      <c r="M51" s="9"/>
-      <c r="N51" s="9"/>
-      <c r="O51" s="9"/>
-      <c r="P51" s="9"/>
-      <c r="Q51" s="9"/>
-      <c r="R51" s="9"/>
-      <c r="S51" s="9"/>
-      <c r="T51" s="9"/>
+      <c r="A51" s="23"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="23"/>
+      <c r="H51" s="23"/>
+      <c r="I51" s="23"/>
+      <c r="J51" s="23"/>
+      <c r="K51" s="23"/>
+      <c r="L51" s="23"/>
+      <c r="M51" s="23"/>
+      <c r="N51" s="23"/>
+      <c r="O51" s="23"/>
+      <c r="P51" s="23"/>
+      <c r="Q51" s="23"/>
+      <c r="R51" s="23"/>
+      <c r="S51" s="23"/>
+      <c r="T51" s="23"/>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
-      <c r="M52" s="9"/>
-      <c r="N52" s="9"/>
-      <c r="O52" s="9"/>
-      <c r="P52" s="9"/>
-      <c r="Q52" s="9"/>
-      <c r="R52" s="9"/>
-      <c r="S52" s="9"/>
-      <c r="T52" s="9"/>
+      <c r="A52" s="23"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="23"/>
+      <c r="I52" s="23"/>
+      <c r="J52" s="23"/>
+      <c r="K52" s="23"/>
+      <c r="L52" s="23"/>
+      <c r="M52" s="23"/>
+      <c r="N52" s="23"/>
+      <c r="O52" s="23"/>
+      <c r="P52" s="23"/>
+      <c r="Q52" s="23"/>
+      <c r="R52" s="23"/>
+      <c r="S52" s="23"/>
+      <c r="T52" s="23"/>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9"/>
-      <c r="K53" s="9"/>
-      <c r="L53" s="9"/>
-      <c r="M53" s="9"/>
-      <c r="N53" s="9"/>
-      <c r="O53" s="9"/>
-      <c r="P53" s="9"/>
-      <c r="Q53" s="9"/>
-      <c r="R53" s="9"/>
-      <c r="S53" s="9"/>
-      <c r="T53" s="9"/>
+      <c r="A53" s="23"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="23"/>
+      <c r="E53" s="23"/>
+      <c r="F53" s="23"/>
+      <c r="G53" s="23"/>
+      <c r="H53" s="23"/>
+      <c r="I53" s="23"/>
+      <c r="J53" s="23"/>
+      <c r="K53" s="23"/>
+      <c r="L53" s="23"/>
+      <c r="M53" s="23"/>
+      <c r="N53" s="23"/>
+      <c r="O53" s="23"/>
+      <c r="P53" s="23"/>
+      <c r="Q53" s="23"/>
+      <c r="R53" s="23"/>
+      <c r="S53" s="23"/>
+      <c r="T53" s="23"/>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
-      <c r="M54" s="9"/>
-      <c r="N54" s="9"/>
-      <c r="O54" s="9"/>
-      <c r="P54" s="9"/>
-      <c r="Q54" s="9"/>
-      <c r="R54" s="9"/>
-      <c r="S54" s="9"/>
-      <c r="T54" s="9"/>
+      <c r="A54" s="23"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="23"/>
+      <c r="H54" s="23"/>
+      <c r="I54" s="23"/>
+      <c r="J54" s="23"/>
+      <c r="K54" s="23"/>
+      <c r="L54" s="23"/>
+      <c r="M54" s="23"/>
+      <c r="N54" s="23"/>
+      <c r="O54" s="23"/>
+      <c r="P54" s="23"/>
+      <c r="Q54" s="23"/>
+      <c r="R54" s="23"/>
+      <c r="S54" s="23"/>
+      <c r="T54" s="23"/>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A55" s="9"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
-      <c r="K55" s="9"/>
-      <c r="L55" s="9"/>
-      <c r="M55" s="9"/>
-      <c r="N55" s="9"/>
-      <c r="O55" s="9"/>
-      <c r="P55" s="9"/>
-      <c r="Q55" s="9"/>
-      <c r="R55" s="9"/>
-      <c r="S55" s="9"/>
-      <c r="T55" s="9"/>
+      <c r="A55" s="23"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
+      <c r="H55" s="23"/>
+      <c r="I55" s="23"/>
+      <c r="J55" s="23"/>
+      <c r="K55" s="23"/>
+      <c r="L55" s="23"/>
+      <c r="M55" s="23"/>
+      <c r="N55" s="23"/>
+      <c r="O55" s="23"/>
+      <c r="P55" s="23"/>
+      <c r="Q55" s="23"/>
+      <c r="R55" s="23"/>
+      <c r="S55" s="23"/>
+      <c r="T55" s="23"/>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A56" s="9"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
-      <c r="K56" s="9"/>
-      <c r="L56" s="9"/>
-      <c r="M56" s="9"/>
-      <c r="N56" s="9"/>
-      <c r="O56" s="9"/>
-      <c r="P56" s="9"/>
-      <c r="Q56" s="9"/>
-      <c r="R56" s="9"/>
-      <c r="S56" s="9"/>
-      <c r="T56" s="9"/>
+      <c r="A56" s="23"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="23"/>
+      <c r="I56" s="23"/>
+      <c r="J56" s="23"/>
+      <c r="K56" s="23"/>
+      <c r="L56" s="23"/>
+      <c r="M56" s="23"/>
+      <c r="N56" s="23"/>
+      <c r="O56" s="23"/>
+      <c r="P56" s="23"/>
+      <c r="Q56" s="23"/>
+      <c r="R56" s="23"/>
+      <c r="S56" s="23"/>
+      <c r="T56" s="23"/>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A57" s="9"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
-      <c r="K57" s="9"/>
-      <c r="L57" s="9"/>
-      <c r="M57" s="9"/>
-      <c r="N57" s="9"/>
-      <c r="O57" s="9"/>
-      <c r="P57" s="9"/>
-      <c r="Q57" s="9"/>
-      <c r="R57" s="9"/>
-      <c r="S57" s="9"/>
-      <c r="T57" s="9"/>
+      <c r="A57" s="23"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="23"/>
+      <c r="F57" s="23"/>
+      <c r="G57" s="23"/>
+      <c r="H57" s="23"/>
+      <c r="I57" s="23"/>
+      <c r="J57" s="23"/>
+      <c r="K57" s="23"/>
+      <c r="L57" s="23"/>
+      <c r="M57" s="23"/>
+      <c r="N57" s="23"/>
+      <c r="O57" s="23"/>
+      <c r="P57" s="23"/>
+      <c r="Q57" s="23"/>
+      <c r="R57" s="23"/>
+      <c r="S57" s="23"/>
+      <c r="T57" s="23"/>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A58" s="9"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
-      <c r="K58" s="9"/>
-      <c r="L58" s="9"/>
-      <c r="M58" s="9"/>
-      <c r="N58" s="9"/>
-      <c r="O58" s="9"/>
-      <c r="P58" s="9"/>
-      <c r="Q58" s="9"/>
-      <c r="R58" s="9"/>
-      <c r="S58" s="9"/>
-      <c r="T58" s="9"/>
+      <c r="A58" s="23"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="23"/>
+      <c r="H58" s="23"/>
+      <c r="I58" s="23"/>
+      <c r="J58" s="23"/>
+      <c r="K58" s="23"/>
+      <c r="L58" s="23"/>
+      <c r="M58" s="23"/>
+      <c r="N58" s="23"/>
+      <c r="O58" s="23"/>
+      <c r="P58" s="23"/>
+      <c r="Q58" s="23"/>
+      <c r="R58" s="23"/>
+      <c r="S58" s="23"/>
+      <c r="T58" s="23"/>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A59" s="9"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="9"/>
-      <c r="J59" s="9"/>
-      <c r="K59" s="9"/>
-      <c r="L59" s="9"/>
-      <c r="M59" s="9"/>
-      <c r="N59" s="9"/>
-      <c r="O59" s="9"/>
-      <c r="P59" s="9"/>
-      <c r="Q59" s="9"/>
-      <c r="R59" s="9"/>
-      <c r="S59" s="9"/>
-      <c r="T59" s="9"/>
+      <c r="A59" s="23"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="23"/>
+      <c r="H59" s="23"/>
+      <c r="I59" s="23"/>
+      <c r="J59" s="23"/>
+      <c r="K59" s="23"/>
+      <c r="L59" s="23"/>
+      <c r="M59" s="23"/>
+      <c r="N59" s="23"/>
+      <c r="O59" s="23"/>
+      <c r="P59" s="23"/>
+      <c r="Q59" s="23"/>
+      <c r="R59" s="23"/>
+      <c r="S59" s="23"/>
+      <c r="T59" s="23"/>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A60" s="9"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="9"/>
-      <c r="J60" s="9"/>
-      <c r="K60" s="9"/>
-      <c r="L60" s="9"/>
-      <c r="M60" s="9"/>
-      <c r="N60" s="9"/>
-      <c r="O60" s="9"/>
-      <c r="P60" s="9"/>
-      <c r="Q60" s="9"/>
-      <c r="R60" s="9"/>
-      <c r="S60" s="9"/>
-      <c r="T60" s="9"/>
+      <c r="A60" s="23"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="23"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="23"/>
+      <c r="H60" s="23"/>
+      <c r="I60" s="23"/>
+      <c r="J60" s="23"/>
+      <c r="K60" s="23"/>
+      <c r="L60" s="23"/>
+      <c r="M60" s="23"/>
+      <c r="N60" s="23"/>
+      <c r="O60" s="23"/>
+      <c r="P60" s="23"/>
+      <c r="Q60" s="23"/>
+      <c r="R60" s="23"/>
+      <c r="S60" s="23"/>
+      <c r="T60" s="23"/>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A61" s="9"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="9"/>
-      <c r="J61" s="9"/>
-      <c r="K61" s="9"/>
-      <c r="L61" s="9"/>
-      <c r="M61" s="9"/>
-      <c r="N61" s="9"/>
-      <c r="O61" s="9"/>
-      <c r="P61" s="9"/>
-      <c r="Q61" s="9"/>
-      <c r="R61" s="9"/>
-      <c r="S61" s="9"/>
-      <c r="T61" s="9"/>
+      <c r="A61" s="23"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="23"/>
+      <c r="D61" s="23"/>
+      <c r="E61" s="23"/>
+      <c r="F61" s="23"/>
+      <c r="G61" s="23"/>
+      <c r="H61" s="23"/>
+      <c r="I61" s="23"/>
+      <c r="J61" s="23"/>
+      <c r="K61" s="23"/>
+      <c r="L61" s="23"/>
+      <c r="M61" s="23"/>
+      <c r="N61" s="23"/>
+      <c r="O61" s="23"/>
+      <c r="P61" s="23"/>
+      <c r="Q61" s="23"/>
+      <c r="R61" s="23"/>
+      <c r="S61" s="23"/>
+      <c r="T61" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="12">
